--- a/AmazonAutomation/testdata/Book1.xlsx
+++ b/AmazonAutomation/testdata/Book1.xlsx
@@ -3,98 +3,74 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suraj kumar meher\OneDrive\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{340C2FAD-E81A-4491-A362-C2E63B7A09A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{E1E2964E-E5B6-46CC-86B4-0A2826CC5148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{8F1FE74E-7E24-4B34-8382-7137BC87A75A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:R8"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
-  <si>
-    <t>BookName</t>
-  </si>
-  <si>
-    <t>purchased_date</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Selenium</t>
-  </si>
-  <si>
-    <t>29th Dec 2019</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Java</t>
-  </si>
-  <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>Mt</t>
-  </si>
-  <si>
-    <t>30th Dec 2020</t>
-  </si>
-  <si>
-    <t>31st Dec 2021</t>
-  </si>
-  <si>
-    <t>4th Dec 2022</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>China</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>Anjali</t>
+  </si>
+  <si>
+    <t>Mysore</t>
+  </si>
+  <si>
+    <t>field</t>
+  </si>
+  <si>
+    <t>salary</t>
+  </si>
+  <si>
+    <t>DevOps</t>
+  </si>
+  <si>
+    <t>Developer</t>
+  </si>
+  <si>
+    <t>Hayati</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>Nagraj</t>
+  </si>
+  <si>
+    <t>Madurai</t>
+  </si>
+  <si>
+    <t>Town</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -435,17 +411,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5F23366-1114-4369-AC3C-1478B2EFE5F4}">
-  <dimension ref="A1:D5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE77DC44-9800-4240-A5D9-6C4C86B10CDD}">
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -453,70 +423,84 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>50000</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>300</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>70000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="C3">
-        <v>400</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
+      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4">
+        <v>60000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>599</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>200</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
+      <c r="E5">
+        <v>90000</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>